--- a/415-rc---harmonisation-des-value-sets-et-code-systems/ig/ValueSet-tddui-encounter-type.xlsx
+++ b/415-rc---harmonisation-des-value-sets-et-code-systems/ig/ValueSet-tddui-encounter-type.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-28T15:51:30+00:00</t>
+    <t>2026-02-02T09:49:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/415-rc---harmonisation-des-value-sets-et-code-systems/ig/ValueSet-tddui-encounter-type.xlsx
+++ b/415-rc---harmonisation-des-value-sets-et-code-systems/ig/ValueSet-tddui-encounter-type.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-02T09:49:54+00:00</t>
+    <t>2026-02-02T14:44:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/415-rc---harmonisation-des-value-sets-et-code-systems/ig/ValueSet-tddui-encounter-type.xlsx
+++ b/415-rc---harmonisation-des-value-sets-et-code-systems/ig/ValueSet-tddui-encounter-type.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-02T14:44:55+00:00</t>
+    <t>2026-02-04T16:15:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/415-rc---harmonisation-des-value-sets-et-code-systems/ig/ValueSet-tddui-encounter-type.xlsx
+++ b/415-rc---harmonisation-des-value-sets-et-code-systems/ig/ValueSet-tddui-encounter-type.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-04T16:15:13+00:00</t>
+    <t>2026-02-05T08:25:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -87,7 +87,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>ValueSet for TDDUI Encounter's types</t>
+    <t>ValueSet pour la définition des codes de type de séjour</t>
   </si>
   <si>
     <t>Purpose</t>
